--- a/public/templates/VTPC-Market-Data-Template.xlsx
+++ b/public/templates/VTPC-Market-Data-Template.xlsx
@@ -189,7 +189,7 @@
     <t>Raichur</t>
   </si>
   <si>
-    <t>Ramanagara</t>
+    <t>Bangalore South (Ramanagara)</t>
   </si>
   <si>
     <t>Shivamogga</t>
